--- a/artfynd/S 346-2026 artfynd.xlsx
+++ b/artfynd/S 346-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AZ63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,58 +802,65 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/223822</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120968120</v>
+        <v>134835639</v>
       </c>
       <c r="B3" t="n">
-        <v>57141</v>
+        <v>106437</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>674</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Michx.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>NV om Hofors, Dlr</t>
+          <t>Åsbotten, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563829</v>
+        <v>563919</v>
       </c>
       <c r="R3" t="n">
-        <v>6716127</v>
+        <v>6715819</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,27 +887,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>08:41</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>08:41</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Mycket spillning runtom natträden också, betad talar. Calluna AB SKH0013b</t>
+          <t>Återfynd,</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,19 +912,24 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marta Lomas Vega</t>
+          <t>Dennis Nyström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marta Lomas Vega</t>
+          <t>Dennis Nyström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134835639</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120968124</v>
+        <v>120968120</v>
       </c>
       <c r="B4" t="n">
         <v>57141</v>
@@ -953,7 +960,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -967,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563643</v>
+        <v>563829</v>
       </c>
       <c r="R4" t="n">
-        <v>6716138</v>
+        <v>6716127</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,12 +1019,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Tre korvar. Calluna AB SKH0013b</t>
+          <t>Mycket spillning runtom natträden också, betad talar. Calluna AB SKH0013b</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,10 +1048,15 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968120</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120968131</v>
+        <v>120968124</v>
       </c>
       <c r="B5" t="n">
         <v>57141</v>
@@ -1075,7 +1087,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1089,10 +1101,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563537</v>
+        <v>563643</v>
       </c>
       <c r="R5" t="n">
-        <v>6716133</v>
+        <v>6716138</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,7 +1136,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1134,12 +1146,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Calluna AB SKH0013b</t>
+          <t>Tre korvar. Calluna AB SKH0013b</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,10 +1175,15 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968124</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120968140</v>
+        <v>120968131</v>
       </c>
       <c r="B6" t="n">
         <v>57141</v>
@@ -1197,7 +1214,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1211,10 +1228,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563541</v>
+        <v>563537</v>
       </c>
       <c r="R6" t="n">
-        <v>6715978</v>
+        <v>6716133</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1246,7 +1263,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:07</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1256,12 +1273,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:07</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>En korv. Calluna AB SKH0013b</t>
+          <t>Calluna AB SKH0013b</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,10 +1302,15 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968131</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120968141</v>
+        <v>120968140</v>
       </c>
       <c r="B7" t="n">
         <v>57141</v>
@@ -1319,7 +1341,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1333,10 +1355,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563582</v>
+        <v>563541</v>
       </c>
       <c r="R7" t="n">
-        <v>6715938</v>
+        <v>6715978</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1368,7 +1390,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:03</t>
+          <t>07:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1378,12 +1400,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:03</t>
+          <t>07:07</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>3 fler fjädrar. Calluna AB SKH0013b</t>
+          <t>En korv. Calluna AB SKH0013b</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1407,10 +1429,15 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968140</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120968142</v>
+        <v>120968141</v>
       </c>
       <c r="B8" t="n">
         <v>57141</v>
@@ -1441,7 +1468,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1455,10 +1482,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563583</v>
+        <v>563582</v>
       </c>
       <c r="R8" t="n">
-        <v>6715940</v>
+        <v>6715938</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1490,7 +1517,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1500,12 +1527,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:03</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Calluna AB SKH0013b</t>
+          <t>3 fler fjädrar. Calluna AB SKH0013b</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1529,10 +1556,15 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968141</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120968146</v>
+        <v>120968142</v>
       </c>
       <c r="B9" t="n">
         <v>57141</v>
@@ -1561,14 +1593,9 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1582,10 +1609,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563642</v>
+        <v>563583</v>
       </c>
       <c r="R9" t="n">
-        <v>6715949</v>
+        <v>6715940</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1617,7 +1644,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>06:55</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1627,12 +1654,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>06:55</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ser utt som ett område tjäder använder som spelplats. Calluna AB SKH0013b</t>
+          <t>Calluna AB SKH0013b</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1656,10 +1683,15 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968142</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120968147</v>
+        <v>120968146</v>
       </c>
       <c r="B10" t="n">
         <v>57141</v>
@@ -1688,9 +1720,14 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1707,7 +1744,7 @@
         <v>563642</v>
       </c>
       <c r="R10" t="n">
-        <v>6715951</v>
+        <v>6715949</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1739,7 +1776,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1749,12 +1786,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:55</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Få spillningar spred sig. Calluna AB SKH0013b</t>
+          <t>Ser utt som ett område tjäder använder som spelplats. Calluna AB SKH0013b</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1778,10 +1815,15 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968146</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120968148</v>
+        <v>120968147</v>
       </c>
       <c r="B11" t="n">
         <v>57141</v>
@@ -1826,10 +1868,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563618</v>
+        <v>563642</v>
       </c>
       <c r="R11" t="n">
-        <v>6715967</v>
+        <v>6715951</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1861,7 +1903,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>06:47</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1871,12 +1913,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>06:47</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Mycket äldre spillning.Calluna AB SKH0013b</t>
+          <t>Få spillningar spred sig. Calluna AB SKH0013b</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1900,10 +1942,15 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968147</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120968150</v>
+        <v>120968148</v>
       </c>
       <c r="B12" t="n">
         <v>57141</v>
@@ -1948,10 +1995,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563613</v>
+        <v>563618</v>
       </c>
       <c r="R12" t="n">
-        <v>6715943</v>
+        <v>6715967</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1983,7 +2030,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1993,12 +2040,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:47</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Mycket spillning bredvid betad tal, även vinterspillning. Calluna AB SKH0013b</t>
+          <t>Mycket äldre spillning.Calluna AB SKH0013b</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2022,10 +2069,15 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968148</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120968152</v>
+        <v>120968150</v>
       </c>
       <c r="B13" t="n">
         <v>57141</v>
@@ -2070,10 +2122,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563615</v>
+        <v>563613</v>
       </c>
       <c r="R13" t="n">
-        <v>6715843</v>
+        <v>6715943</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2105,7 +2157,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2115,12 +2167,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Bild finns. Calluna AB SKH0013b</t>
+          <t>Mycket spillning bredvid betad tal, även vinterspillning. Calluna AB SKH0013b</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2144,10 +2196,15 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968150</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120968156</v>
+        <v>120968152</v>
       </c>
       <c r="B14" t="n">
         <v>57141</v>
@@ -2178,7 +2235,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2192,10 +2249,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563529</v>
+        <v>563615</v>
       </c>
       <c r="R14" t="n">
-        <v>6715788</v>
+        <v>6715843</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2227,7 +2284,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>06:24</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2237,12 +2294,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>06:24</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>1 spillning med vit kant. Calluna AB SKH0013b</t>
+          <t>Bild finns. Calluna AB SKH0013b</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2266,10 +2323,15 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968152</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120968171</v>
+        <v>120968156</v>
       </c>
       <c r="B15" t="n">
         <v>57141</v>
@@ -2314,10 +2376,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563330</v>
+        <v>563529</v>
       </c>
       <c r="R15" t="n">
-        <v>6715469</v>
+        <v>6715788</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2344,27 +2406,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>06:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>06:24</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På vägen. Calluna AB SKH0013b</t>
+          <t>1 spillning med vit kant. Calluna AB SKH0013b</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2388,10 +2450,15 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968156</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120968174</v>
+        <v>120968171</v>
       </c>
       <c r="B16" t="n">
         <v>57141</v>
@@ -2422,7 +2489,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2436,10 +2503,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563303</v>
+        <v>563330</v>
       </c>
       <c r="R16" t="n">
-        <v>6715579</v>
+        <v>6715469</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2471,7 +2538,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2481,12 +2548,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Calluna AB SKH0013b</t>
+          <t>På vägen. Calluna AB SKH0013b</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2506,14 +2573,19 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marta Lomas Vega, Dan Wahlborg</t>
+          <t>Marta Lomas Vega</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968171</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120968175</v>
+        <v>120968174</v>
       </c>
       <c r="B17" t="n">
         <v>57141</v>
@@ -2544,7 +2616,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2558,10 +2630,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563262</v>
+        <v>563303</v>
       </c>
       <c r="R17" t="n">
-        <v>6715603</v>
+        <v>6715579</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2593,7 +2665,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2603,7 +2675,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2632,10 +2704,15 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968174</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120968176</v>
+        <v>120968175</v>
       </c>
       <c r="B18" t="n">
         <v>57141</v>
@@ -2666,7 +2743,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2680,10 +2757,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563452</v>
+        <v>563262</v>
       </c>
       <c r="R18" t="n">
-        <v>6715594</v>
+        <v>6715603</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2715,7 +2792,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2725,7 +2802,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2754,10 +2831,15 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968175</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120968178</v>
+        <v>120968176</v>
       </c>
       <c r="B19" t="n">
         <v>57141</v>
@@ -2802,10 +2884,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563456</v>
+        <v>563452</v>
       </c>
       <c r="R19" t="n">
-        <v>6715582</v>
+        <v>6715594</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2837,7 +2919,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2847,7 +2929,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2876,10 +2958,15 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968176</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120968179</v>
+        <v>120968178</v>
       </c>
       <c r="B20" t="n">
         <v>57141</v>
@@ -2910,7 +2997,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2924,10 +3011,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563304</v>
+        <v>563456</v>
       </c>
       <c r="R20" t="n">
-        <v>6715876</v>
+        <v>6715582</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2959,7 +3046,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2969,7 +3056,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2998,10 +3085,15 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968178</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120968186</v>
+        <v>120968179</v>
       </c>
       <c r="B21" t="n">
         <v>57141</v>
@@ -3046,10 +3138,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563425</v>
+        <v>563304</v>
       </c>
       <c r="R21" t="n">
-        <v>6716079</v>
+        <v>6715876</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3081,7 +3173,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>06:49</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3091,7 +3183,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>06:49</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3120,10 +3212,15 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968179</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120968190</v>
+        <v>120968186</v>
       </c>
       <c r="B22" t="n">
         <v>57141</v>
@@ -3168,10 +3265,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563446</v>
+        <v>563425</v>
       </c>
       <c r="R22" t="n">
-        <v>6716061</v>
+        <v>6716079</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3203,7 +3300,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>06:46</t>
+          <t>06:49</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3213,7 +3310,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>06:46</t>
+          <t>06:49</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3242,10 +3339,15 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968186</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120968203</v>
+        <v>120968190</v>
       </c>
       <c r="B23" t="n">
         <v>57141</v>
@@ -3276,7 +3378,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3290,10 +3392,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563288</v>
+        <v>563446</v>
       </c>
       <c r="R23" t="n">
-        <v>6715472</v>
+        <v>6716061</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3325,7 +3427,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3335,7 +3437,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:46</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3360,14 +3462,19 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marta Lomas Vega</t>
+          <t>Marta Lomas Vega, Dan Wahlborg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968190</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120968204</v>
+        <v>120968203</v>
       </c>
       <c r="B24" t="n">
         <v>57141</v>
@@ -3412,10 +3519,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>563278</v>
+        <v>563288</v>
       </c>
       <c r="R24" t="n">
-        <v>6715479</v>
+        <v>6715472</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3447,7 +3554,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>06:09</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3457,7 +3564,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>06:09</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3486,10 +3593,15 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968203</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120968205</v>
+        <v>120968204</v>
       </c>
       <c r="B25" t="n">
         <v>57141</v>
@@ -3520,7 +3632,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3534,10 +3646,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>563104</v>
+        <v>563278</v>
       </c>
       <c r="R25" t="n">
-        <v>6715792</v>
+        <v>6715479</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3569,7 +3681,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>06:07</t>
+          <t>06:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3579,7 +3691,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>06:07</t>
+          <t>06:09</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3604,14 +3716,19 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marta Lomas Vega, Dan Wahlborg</t>
+          <t>Marta Lomas Vega</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968204</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120968206</v>
+        <v>120968205</v>
       </c>
       <c r="B26" t="n">
         <v>57141</v>
@@ -3642,7 +3759,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3656,10 +3773,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>563252</v>
+        <v>563104</v>
       </c>
       <c r="R26" t="n">
-        <v>6715497</v>
+        <v>6715792</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3691,7 +3808,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>06:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3701,7 +3818,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>06:07</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3726,14 +3843,19 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marta Lomas Vega</t>
+          <t>Marta Lomas Vega, Dan Wahlborg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968205</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120968208</v>
+        <v>120968206</v>
       </c>
       <c r="B27" t="n">
         <v>57141</v>
@@ -3764,7 +3886,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3778,10 +3900,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>563233</v>
+        <v>563252</v>
       </c>
       <c r="R27" t="n">
-        <v>6715513</v>
+        <v>6715497</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3813,7 +3935,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3823,7 +3945,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3852,10 +3974,15 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968206</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120968209</v>
+        <v>120968208</v>
       </c>
       <c r="B28" t="n">
         <v>57141</v>
@@ -3886,7 +4013,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3900,10 +4027,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>563141</v>
+        <v>563233</v>
       </c>
       <c r="R28" t="n">
-        <v>6715660</v>
+        <v>6715513</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3935,7 +4062,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3945,7 +4072,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3970,14 +4097,19 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marta Lomas Vega, Dan Wahlborg</t>
+          <t>Marta Lomas Vega</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968208</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120968210</v>
+        <v>120968209</v>
       </c>
       <c r="B29" t="n">
         <v>57141</v>
@@ -4022,10 +4154,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>563218</v>
+        <v>563141</v>
       </c>
       <c r="R29" t="n">
-        <v>6715543</v>
+        <v>6715660</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4057,7 +4189,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4067,7 +4199,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4092,14 +4224,19 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marta Lomas Vega</t>
+          <t>Marta Lomas Vega, Dan Wahlborg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968209</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120968211</v>
+        <v>120968210</v>
       </c>
       <c r="B30" t="n">
         <v>57141</v>
@@ -4144,10 +4281,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>563203</v>
+        <v>563218</v>
       </c>
       <c r="R30" t="n">
-        <v>6715568</v>
+        <v>6715543</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4179,7 +4316,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4189,7 +4326,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4218,10 +4355,15 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968210</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120968213</v>
+        <v>120968211</v>
       </c>
       <c r="B31" t="n">
         <v>57141</v>
@@ -4252,7 +4394,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4266,10 +4408,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>563248</v>
+        <v>563203</v>
       </c>
       <c r="R31" t="n">
-        <v>6715564</v>
+        <v>6715568</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4301,7 +4443,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4311,12 +4453,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Alla våspilllningar på den här platsen har vita kanter men inte alla är korta korvar; det finns korta och långa korvar. Calluna AB SKH0013b</t>
+          <t>Calluna AB SKH0013b</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4340,10 +4482,15 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968211</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120968214</v>
+        <v>120968213</v>
       </c>
       <c r="B32" t="n">
         <v>57141</v>
@@ -4374,7 +4521,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4388,10 +4535,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>563235</v>
+        <v>563248</v>
       </c>
       <c r="R32" t="n">
-        <v>6715575</v>
+        <v>6715564</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4423,7 +4570,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>05:43</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4433,12 +4580,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>05:43</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Få av dem. Calluna AB SKH0013b</t>
+          <t>Alla våspilllningar på den här platsen har vita kanter men inte alla är korta korvar; det finns korta och långa korvar. Calluna AB SKH0013b</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4462,10 +4609,15 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968213</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120968215</v>
+        <v>120968214</v>
       </c>
       <c r="B33" t="n">
         <v>57141</v>
@@ -4510,10 +4662,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>563136</v>
+        <v>563235</v>
       </c>
       <c r="R33" t="n">
-        <v>6715550</v>
+        <v>6715575</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4545,7 +4697,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>05:40</t>
+          <t>05:43</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4555,12 +4707,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>05:40</t>
+          <t>05:43</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Korta korvar med vit kant. Calluna AB SKH0013b</t>
+          <t>Få av dem. Calluna AB SKH0013b</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4580,14 +4732,19 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marta Lomas Vega, Dan Wahlborg</t>
+          <t>Marta Lomas Vega</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968214</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120968217</v>
+        <v>120968215</v>
       </c>
       <c r="B34" t="n">
         <v>57141</v>
@@ -4616,11 +4773,6 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M34" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -4637,10 +4789,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>563200</v>
+        <v>563136</v>
       </c>
       <c r="R34" t="n">
-        <v>6715561</v>
+        <v>6715550</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4672,7 +4824,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>05:34</t>
+          <t>05:40</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4682,12 +4834,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>05:34</t>
+          <t>05:40</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Calluna AB SKH0013b</t>
+          <t>Korta korvar med vit kant. Calluna AB SKH0013b</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4711,10 +4863,15 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968215</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120968218</v>
+        <v>120968217</v>
       </c>
       <c r="B35" t="n">
         <v>57141</v>
@@ -4743,6 +4900,11 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -4759,10 +4921,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>563204</v>
+        <v>563200</v>
       </c>
       <c r="R35" t="n">
-        <v>6715558</v>
+        <v>6715561</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4794,7 +4956,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>05:33</t>
+          <t>05:34</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4804,7 +4966,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>05:33</t>
+          <t>05:34</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4833,10 +4995,15 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968217</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120968219</v>
+        <v>120968218</v>
       </c>
       <c r="B36" t="n">
         <v>57141</v>
@@ -4881,10 +5048,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>563257</v>
+        <v>563204</v>
       </c>
       <c r="R36" t="n">
-        <v>6715544</v>
+        <v>6715558</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4916,7 +5083,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>05:33</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4926,7 +5093,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>05:33</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -4951,14 +5118,19 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marta Lomas Vega</t>
+          <t>Marta Lomas Vega, Dan Wahlborg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968218</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120968220</v>
+        <v>120968219</v>
       </c>
       <c r="B37" t="n">
         <v>57141</v>
@@ -4989,7 +5161,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -5003,10 +5175,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>563268</v>
+        <v>563257</v>
       </c>
       <c r="R37" t="n">
-        <v>6715526</v>
+        <v>6715544</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5038,7 +5210,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>05:28</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5048,12 +5220,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>05:28</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Vårspillingar med vita kanter. Calluna AB SKH0013b</t>
+          <t>Calluna AB SKH0013b</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5077,13 +5249,18 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968219</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120902611</v>
+        <v>120968220</v>
       </c>
       <c r="B38" t="n">
-        <v>57144</v>
+        <v>57141</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5091,41 +5268,32 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5134,10 +5302,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>563878</v>
+        <v>563268</v>
       </c>
       <c r="R38" t="n">
-        <v>6715743</v>
+        <v>6715526</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5164,27 +5332,27 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>05:53</t>
+          <t>05:28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>05:53</t>
+          <t>05:28</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Spel hördes, Calluna AB, SKH013b</t>
+          <t>Vårspillingar med vita kanter. Calluna AB SKH0013b</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5208,10 +5376,15 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968220</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120902614</v>
+        <v>120902611</v>
       </c>
       <c r="B39" t="n">
         <v>57144</v>
@@ -5259,21 +5432,16 @@
           <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>NV om Hofors, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>563685</v>
+        <v>563878</v>
       </c>
       <c r="R39" t="n">
-        <v>6715485</v>
+        <v>6715743</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5305,7 +5473,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>05:24</t>
+          <t>05:53</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5315,12 +5483,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>05:24</t>
+          <t>05:53</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>En hane flyger över trädtopparna mot sjö området , Calluna AB, SKH013b</t>
+          <t>Spel hördes, Calluna AB, SKH013b</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5344,10 +5512,15 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120902611</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120968113</v>
+        <v>120902614</v>
       </c>
       <c r="B40" t="n">
         <v>57144</v>
@@ -5375,10 +5548,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5392,10 +5579,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>563838</v>
+        <v>563685</v>
       </c>
       <c r="R40" t="n">
-        <v>6716326</v>
+        <v>6715485</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5427,7 +5614,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>05:24</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5437,12 +5624,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>05:24</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Calluna AB SKH0013b</t>
+          <t>En hane flyger över trädtopparna mot sjö området , Calluna AB, SKH013b</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5466,10 +5653,15 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120902614</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120968117</v>
+        <v>120968113</v>
       </c>
       <c r="B41" t="n">
         <v>57144</v>
@@ -5500,7 +5692,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -5514,10 +5706,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>563828</v>
+        <v>563838</v>
       </c>
       <c r="R41" t="n">
-        <v>6716293</v>
+        <v>6716326</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5549,7 +5741,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5559,12 +5751,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>En korv. Calluna AB SKH0013b</t>
+          <t>Calluna AB SKH0013b</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5588,10 +5780,15 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968113</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120968118</v>
+        <v>120968117</v>
       </c>
       <c r="B42" t="n">
         <v>57144</v>
@@ -5622,7 +5819,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -5636,10 +5833,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>563871</v>
+        <v>563828</v>
       </c>
       <c r="R42" t="n">
-        <v>6716139</v>
+        <v>6716293</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5671,7 +5868,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5681,12 +5878,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Vita kanter. Calluna AB SKH0013b</t>
+          <t>En korv. Calluna AB SKH0013b</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5710,10 +5907,15 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968117</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120968119</v>
+        <v>120968118</v>
       </c>
       <c r="B43" t="n">
         <v>57144</v>
@@ -5744,7 +5946,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5758,10 +5960,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>563843</v>
+        <v>563871</v>
       </c>
       <c r="R43" t="n">
-        <v>6716117</v>
+        <v>6716139</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5793,7 +5995,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5803,12 +6005,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Calluna AB SKH0013b</t>
+          <t>Vita kanter. Calluna AB SKH0013b</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5832,10 +6034,15 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968118</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120968121</v>
+        <v>120968119</v>
       </c>
       <c r="B44" t="n">
         <v>57144</v>
@@ -5864,14 +6071,9 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5885,10 +6087,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>563743</v>
+        <v>563843</v>
       </c>
       <c r="R44" t="n">
-        <v>6716164</v>
+        <v>6716117</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5920,7 +6122,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5930,7 +6132,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -5959,10 +6161,15 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968119</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120968126</v>
+        <v>120968121</v>
       </c>
       <c r="B45" t="n">
         <v>57144</v>
@@ -5991,6 +6198,11 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -6007,10 +6219,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>563543</v>
+        <v>563743</v>
       </c>
       <c r="R45" t="n">
-        <v>6716208</v>
+        <v>6716164</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6042,7 +6254,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6052,7 +6264,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -6081,10 +6293,15 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968121</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120968128</v>
+        <v>120968126</v>
       </c>
       <c r="B46" t="n">
         <v>57144</v>
@@ -6115,7 +6332,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6129,10 +6346,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>563485</v>
+        <v>563543</v>
       </c>
       <c r="R46" t="n">
-        <v>6716246</v>
+        <v>6716208</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6164,7 +6381,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6174,12 +6391,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Samma typ som tidigare. Calluna AB SKH0013b</t>
+          <t>Calluna AB SKH0013b</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6203,10 +6420,15 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968126</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120968130</v>
+        <v>120968128</v>
       </c>
       <c r="B47" t="n">
         <v>57144</v>
@@ -6251,10 +6473,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>563465</v>
+        <v>563485</v>
       </c>
       <c r="R47" t="n">
-        <v>6716196</v>
+        <v>6716246</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6286,7 +6508,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6296,12 +6518,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Mycket spillning, hörs orrspel hela tiden. Calluna AB SKH0013b</t>
+          <t>Samma typ som tidigare. Calluna AB SKH0013b</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6325,10 +6547,15 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968128</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120968192</v>
+        <v>120968130</v>
       </c>
       <c r="B48" t="n">
         <v>57144</v>
@@ -6359,7 +6586,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -6373,10 +6600,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>563398</v>
+        <v>563465</v>
       </c>
       <c r="R48" t="n">
-        <v>6715956</v>
+        <v>6716196</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6403,27 +6630,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Äldre spillning och fjädrar efter slagen höna. Calluna AB SKH0013b</t>
+          <t>Mycket spillning, hörs orrspel hela tiden. Calluna AB SKH0013b</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6443,17 +6670,22 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marta Lomas Vega, Dan Wahlborg</t>
+          <t>Marta Lomas Vega</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968130</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>112616248</v>
+        <v>120968192</v>
       </c>
       <c r="B49" t="n">
-        <v>56823</v>
+        <v>57144</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6461,51 +6693,44 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>205992</v>
+        <v>102613</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>autobox med höghastighetsinspelning</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hofors/Hedemora, Dlr</t>
+          <t>NV om Hofors, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>563646</v>
+        <v>563398</v>
       </c>
       <c r="R49" t="n">
-        <v>6715329</v>
+        <v>6715956</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6532,17 +6757,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2023-07-07</t>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Autobox ID K2 230705</t>
+          <t>Äldre spillning och fjädrar efter slagen höna. Calluna AB SKH0013b</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6557,22 +6792,27 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Åsa Duell</t>
+          <t>Marta Lomas Vega</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Åsa Duell</t>
+          <t>Marta Lomas Vega, Dan Wahlborg</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968192</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>112616166</v>
+        <v>134836007</v>
       </c>
       <c r="B50" t="n">
-        <v>56816</v>
+        <v>102318</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6580,51 +6820,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>205998</v>
+        <v>221235</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
-        </is>
-      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hedtjärnen, Hofors/Hedemora, Dlr</t>
+          <t>Åsbotten, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>563646</v>
+        <v>563919</v>
       </c>
       <c r="R50" t="n">
-        <v>6715329</v>
+        <v>6715819</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6651,17 +6882,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2023-07-07</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Autobox ID K2 230705</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6676,22 +6902,27 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Åsa Duell</t>
+          <t>Dennis Nyström</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Åsa Duell</t>
+          <t>Dennis Nyström</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134836007</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120968196</v>
+        <v>112616248</v>
       </c>
       <c r="B51" t="n">
-        <v>57141</v>
+        <v>56823</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6699,44 +6930,51 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>205992</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>NV om Hofors, Dlr</t>
+          <t>Hedtjärnen, Hofors/Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>563306</v>
+        <v>563646</v>
       </c>
       <c r="R51" t="n">
-        <v>6715353</v>
+        <v>6715329</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6763,27 +7001,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>06:28</t>
+          <t>2023-07-05</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>06:28</t>
+          <t>2023-07-07</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Inte så mycket vita kanter. Calluna AB SKH0013b</t>
+          <t>Autobox ID K2 230705</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6798,67 +7026,79 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marta Lomas Vega</t>
+          <t>Åsa Duell</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marta Lomas Vega</t>
+          <t>Åsa Duell</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112616248</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120968197</v>
+        <v>112616166</v>
       </c>
       <c r="B52" t="n">
-        <v>57141</v>
+        <v>56816</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100138</v>
+        <v>205998</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>NV om Hofors, Dlr</t>
+          <t>Hedtjärnen, Hofors/Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>563287</v>
+        <v>563646</v>
       </c>
       <c r="R52" t="n">
-        <v>6715422</v>
+        <v>6715329</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6885,27 +7125,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>06:23</t>
+          <t>2023-07-05</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>06:23</t>
+          <t>2023-07-07</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Många spred sig över. Calluna AB SKH0013b</t>
+          <t>Autobox ID K2 230705</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6920,19 +7150,24 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Marta Lomas Vega</t>
+          <t>Åsa Duell</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Marta Lomas Vega</t>
+          <t>Åsa Duell</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112616166</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120968198</v>
+        <v>120968196</v>
       </c>
       <c r="B53" t="n">
         <v>57141</v>
@@ -6977,10 +7212,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>563292</v>
+        <v>563306</v>
       </c>
       <c r="R53" t="n">
-        <v>6715428</v>
+        <v>6715353</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7012,7 +7247,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:28</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7022,12 +7257,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:28</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Calluna AB SKH0013b</t>
+          <t>Inte så mycket vita kanter. Calluna AB SKH0013b</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7051,10 +7286,15 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968196</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120968200</v>
+        <v>120968197</v>
       </c>
       <c r="B54" t="n">
         <v>57141</v>
@@ -7085,7 +7325,7 @@
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -7099,10 +7339,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>563296</v>
+        <v>563287</v>
       </c>
       <c r="R54" t="n">
-        <v>6715452</v>
+        <v>6715422</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7134,7 +7374,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>06:12</t>
+          <t>06:23</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7144,12 +7384,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>06:12</t>
+          <t>06:23</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På vägen. Calluna AB SKH0013b</t>
+          <t>Många spred sig över. Calluna AB SKH0013b</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7173,10 +7413,15 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968197</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120968202</v>
+        <v>120968198</v>
       </c>
       <c r="B55" t="n">
         <v>57141</v>
@@ -7221,10 +7466,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>563296</v>
+        <v>563292</v>
       </c>
       <c r="R55" t="n">
-        <v>6715455</v>
+        <v>6715428</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7256,7 +7501,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>06:12</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7266,12 +7511,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>06:12</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>fjäder av tjäder. Calluna AB SKH0013b</t>
+          <t>Calluna AB SKH0013b</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7295,10 +7540,15 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968198</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120968173</v>
+        <v>120968200</v>
       </c>
       <c r="B56" t="n">
         <v>57141</v>
@@ -7329,7 +7579,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -7343,10 +7593,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>563077</v>
+        <v>563296</v>
       </c>
       <c r="R56" t="n">
-        <v>6715470</v>
+        <v>6715452</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7378,7 +7628,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7388,7 +7638,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -7417,10 +7667,15 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968200</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120968184</v>
+        <v>120968202</v>
       </c>
       <c r="B57" t="n">
         <v>57141</v>
@@ -7449,11 +7704,9 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -7467,10 +7720,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>563062</v>
+        <v>563296</v>
       </c>
       <c r="R57" t="n">
-        <v>6715433</v>
+        <v>6715455</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7497,27 +7750,27 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Många spillningar runt lite betad tal. Calluna AB SKH0013b</t>
+          <t>fjäder av tjäder. Calluna AB SKH0013b</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7541,10 +7794,15 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968202</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120968185</v>
+        <v>120968173</v>
       </c>
       <c r="B58" t="n">
         <v>57141</v>
@@ -7589,10 +7847,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>563092</v>
+        <v>563077</v>
       </c>
       <c r="R58" t="n">
-        <v>6715410</v>
+        <v>6715470</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7624,7 +7882,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7634,12 +7892,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Calluna AB SKH0013b</t>
+          <t>På vägen. Calluna AB SKH0013b</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7663,10 +7921,15 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968173</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120968188</v>
+        <v>120968184</v>
       </c>
       <c r="B59" t="n">
         <v>57141</v>
@@ -7695,6 +7958,8 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
           <t>äldre spillning</t>
@@ -7711,10 +7976,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>563139</v>
+        <v>563062</v>
       </c>
       <c r="R59" t="n">
-        <v>6715370</v>
+        <v>6715433</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7741,27 +8006,27 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>06:48</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>06:48</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Calluna AB SKH0013b</t>
+          <t>Många spillningar runt lite betad tal. Calluna AB SKH0013b</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7785,10 +8050,15 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968184</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120968189</v>
+        <v>120968185</v>
       </c>
       <c r="B60" t="n">
         <v>57141</v>
@@ -7833,10 +8103,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>563163</v>
+        <v>563092</v>
       </c>
       <c r="R60" t="n">
-        <v>6715357</v>
+        <v>6715410</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7868,7 +8138,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>06:46</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7878,12 +8148,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>06:46</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Lite torr men vit kant , en bara. Calluna AB SKH0013b</t>
+          <t>Calluna AB SKH0013b</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7907,13 +8177,18 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968185</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120902623</v>
+        <v>120968188</v>
       </c>
       <c r="B61" t="n">
-        <v>57144</v>
+        <v>57141</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7921,32 +8196,32 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7955,10 +8230,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>562827</v>
+        <v>563139</v>
       </c>
       <c r="R61" t="n">
-        <v>6715541</v>
+        <v>6715370</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7990,7 +8265,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>07:09</t>
+          <t>06:48</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8000,12 +8275,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>07:09</t>
+          <t>06:48</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Orrspel hördes närmare , Calluna AB, SKH013b</t>
+          <t>Calluna AB SKH0013b</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8029,8 +8304,331 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968188</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>120968189</v>
+      </c>
+      <c r="B62" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>NV om Hofors, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>563163</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6715357</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>06:46</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>06:46</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Lite torr men vit kant , en bara. Calluna AB SKH0013b</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Marta Lomas Vega</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Marta Lomas Vega</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120968189</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>120902623</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>NV om Hofors, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>562827</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6715541</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>07:09</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>07:09</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Orrspel hördes närmare , Calluna AB, SKH013b</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Marta Lomas Vega</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Marta Lomas Vega</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120902623</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 346-2026 artfynd.xlsx
+++ b/artfynd/S 346-2026 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>134835639</v>
       </c>
       <c r="B3" t="n">
-        <v>106437</v>
+        <v>106492</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>134836007</v>
       </c>
       <c r="B50" t="n">
-        <v>102318</v>
+        <v>102367</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/S 346-2026 artfynd.xlsx
+++ b/artfynd/S 346-2026 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>134835639</v>
       </c>
       <c r="B3" t="n">
-        <v>106492</v>
+        <v>106519</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>134836007</v>
       </c>
       <c r="B50" t="n">
-        <v>102367</v>
+        <v>102394</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
